--- a/backend/data/EShop Dataset.xlsx
+++ b/backend/data/EShop Dataset.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1259"/>
+  <dimension ref="A1:U1268"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -82234,9 +82234,594 @@
         <v>test@gmail.com</v>
       </c>
     </row>
+    <row r="1260">
+      <c r="A1260">
+        <v>1131</v>
+      </c>
+      <c r="B1260" t="str">
+        <v>test</v>
+      </c>
+      <c r="C1260" t="str">
+        <v/>
+      </c>
+      <c r="D1260" t="str">
+        <v>123 Ave</v>
+      </c>
+      <c r="E1260" t="str">
+        <v>Arlington</v>
+      </c>
+      <c r="F1260" t="str">
+        <v>US</v>
+      </c>
+      <c r="G1260" t="str">
+        <v/>
+      </c>
+      <c r="H1260" t="str">
+        <v/>
+      </c>
+      <c r="I1260" t="str">
+        <v/>
+      </c>
+      <c r="J1260" t="str">
+        <v/>
+      </c>
+      <c r="K1260" t="str">
+        <v>US</v>
+      </c>
+      <c r="L1260" t="str">
+        <v>Unq605481767US</v>
+      </c>
+      <c r="M1260" t="str">
+        <v>Account Setup</v>
+      </c>
+      <c r="N1260" t="str">
+        <v>0 $</v>
+      </c>
+      <c r="O1260" t="str">
+        <v>2025-12-17T16:23:12.579Z</v>
+      </c>
+      <c r="P1260" t="str">
+        <v>2025-12-17T16:23:12.579Z</v>
+      </c>
+      <c r="Q1260">
+        <v>0</v>
+      </c>
+      <c r="R1260" t="str">
+        <v>US</v>
+      </c>
+      <c r="S1260" t="str">
+        <v>US</v>
+      </c>
+      <c r="T1260" t="str">
+        <v>789456123</v>
+      </c>
+      <c r="U1260" t="str">
+        <v>test2@gmail.com</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261">
+        <v>1132</v>
+      </c>
+      <c r="B1261" t="str">
+        <v>test</v>
+      </c>
+      <c r="C1261" t="str">
+        <v/>
+      </c>
+      <c r="D1261" t="str">
+        <v>123 Ave</v>
+      </c>
+      <c r="E1261" t="str">
+        <v>Arlington</v>
+      </c>
+      <c r="F1261" t="str">
+        <v>United States</v>
+      </c>
+      <c r="G1261" t="str">
+        <v>123456789456120</v>
+      </c>
+      <c r="H1261" t="str">
+        <v>VISA</v>
+      </c>
+      <c r="I1261" t="str">
+        <v>Arlington</v>
+      </c>
+      <c r="J1261" t="str">
+        <v>123 Ave</v>
+      </c>
+      <c r="K1261" t="str">
+        <v>United States</v>
+      </c>
+      <c r="L1261" t="str">
+        <v>Unq941417947US</v>
+      </c>
+      <c r="M1261" t="str">
+        <v>headphones</v>
+      </c>
+      <c r="N1261" t="str">
+        <v>123 $</v>
+      </c>
+      <c r="O1261" t="str">
+        <v>2025-12-17T16:23:50.788Z</v>
+      </c>
+      <c r="P1261" t="str">
+        <v>2025-12-17T16:23:50.788Z</v>
+      </c>
+      <c r="Q1261">
+        <v>1</v>
+      </c>
+      <c r="R1261" t="str">
+        <v>US</v>
+      </c>
+      <c r="S1261" t="str">
+        <v xml:space="preserve"> China</v>
+      </c>
+      <c r="T1261" t="str">
+        <v>789456123</v>
+      </c>
+      <c r="U1261" t="str">
+        <v>test2@gmail.com</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262">
+        <v>1132</v>
+      </c>
+      <c r="B1262" t="str">
+        <v>test</v>
+      </c>
+      <c r="C1262" t="str">
+        <v/>
+      </c>
+      <c r="D1262" t="str">
+        <v>123 Ave</v>
+      </c>
+      <c r="E1262" t="str">
+        <v>Arlington</v>
+      </c>
+      <c r="F1262" t="str">
+        <v>United States</v>
+      </c>
+      <c r="G1262" t="str">
+        <v>123456789456120</v>
+      </c>
+      <c r="H1262" t="str">
+        <v>VISA</v>
+      </c>
+      <c r="I1262" t="str">
+        <v>Arlington</v>
+      </c>
+      <c r="J1262" t="str">
+        <v>123 Ave</v>
+      </c>
+      <c r="K1262" t="str">
+        <v>United States</v>
+      </c>
+      <c r="L1262" t="str">
+        <v>Unq941417947US</v>
+      </c>
+      <c r="M1262" t="str">
+        <v>window</v>
+      </c>
+      <c r="N1262" t="str">
+        <v>32 $</v>
+      </c>
+      <c r="O1262" t="str">
+        <v>2025-12-17T16:23:50.788Z</v>
+      </c>
+      <c r="P1262" t="str">
+        <v>2025-12-17T16:23:50.788Z</v>
+      </c>
+      <c r="Q1262">
+        <v>1</v>
+      </c>
+      <c r="R1262" t="str">
+        <v>US</v>
+      </c>
+      <c r="S1262" t="str">
+        <v xml:space="preserve"> United States</v>
+      </c>
+      <c r="T1262" t="str">
+        <v>789456123</v>
+      </c>
+      <c r="U1262" t="str">
+        <v>test2@gmail.com</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263">
+        <v>1132</v>
+      </c>
+      <c r="B1263" t="str">
+        <v>test</v>
+      </c>
+      <c r="C1263" t="str">
+        <v/>
+      </c>
+      <c r="D1263" t="str">
+        <v>123 Ave</v>
+      </c>
+      <c r="E1263" t="str">
+        <v>Arlington</v>
+      </c>
+      <c r="F1263" t="str">
+        <v>United States</v>
+      </c>
+      <c r="G1263" t="str">
+        <v>123456789456120</v>
+      </c>
+      <c r="H1263" t="str">
+        <v>VISA</v>
+      </c>
+      <c r="I1263" t="str">
+        <v>Arlington</v>
+      </c>
+      <c r="J1263" t="str">
+        <v>123 Ave</v>
+      </c>
+      <c r="K1263" t="str">
+        <v>United States</v>
+      </c>
+      <c r="L1263" t="str">
+        <v>Unq941417947US</v>
+      </c>
+      <c r="M1263" t="str">
+        <v>Tax (7%)</v>
+      </c>
+      <c r="N1263" t="str">
+        <v>10.85 $</v>
+      </c>
+      <c r="O1263" t="str">
+        <v>2025-12-17T16:23:50.788Z</v>
+      </c>
+      <c r="P1263" t="str">
+        <v>2025-12-17T16:23:50.788Z</v>
+      </c>
+      <c r="Q1263">
+        <v>1</v>
+      </c>
+      <c r="R1263" t="str">
+        <v>United States</v>
+      </c>
+      <c r="S1263" t="str">
+        <v>United States</v>
+      </c>
+      <c r="T1263" t="str">
+        <v>789456123</v>
+      </c>
+      <c r="U1263" t="str">
+        <v>test2@gmail.com</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264">
+        <v>1132</v>
+      </c>
+      <c r="B1264" t="str">
+        <v>test</v>
+      </c>
+      <c r="C1264" t="str">
+        <v/>
+      </c>
+      <c r="D1264" t="str">
+        <v>123 Ave</v>
+      </c>
+      <c r="E1264" t="str">
+        <v>Arlington</v>
+      </c>
+      <c r="F1264" t="str">
+        <v>United States</v>
+      </c>
+      <c r="G1264" t="str">
+        <v>123456789456120</v>
+      </c>
+      <c r="H1264" t="str">
+        <v>VISA</v>
+      </c>
+      <c r="I1264" t="str">
+        <v>Arlington</v>
+      </c>
+      <c r="J1264" t="str">
+        <v>123 Ave</v>
+      </c>
+      <c r="K1264" t="str">
+        <v>United States</v>
+      </c>
+      <c r="L1264" t="str">
+        <v>Unq941417947US</v>
+      </c>
+      <c r="M1264" t="str">
+        <v>Delivery Charge</v>
+      </c>
+      <c r="N1264" t="str">
+        <v>12.79 $</v>
+      </c>
+      <c r="O1264" t="str">
+        <v>2025-12-17T16:23:50.788Z</v>
+      </c>
+      <c r="P1264" t="str">
+        <v>2025-12-17T16:23:50.788Z</v>
+      </c>
+      <c r="Q1264">
+        <v>1</v>
+      </c>
+      <c r="R1264" t="str">
+        <v>United States</v>
+      </c>
+      <c r="S1264" t="str">
+        <v>United States</v>
+      </c>
+      <c r="T1264" t="str">
+        <v>789456123</v>
+      </c>
+      <c r="U1264" t="str">
+        <v>test2@gmail.com</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265">
+        <v>1133</v>
+      </c>
+      <c r="B1265" t="str">
+        <v>test</v>
+      </c>
+      <c r="C1265" t="str">
+        <v/>
+      </c>
+      <c r="D1265" t="str">
+        <v xml:space="preserve">123 Ave </v>
+      </c>
+      <c r="E1265" t="str">
+        <v>Arlington</v>
+      </c>
+      <c r="F1265" t="str">
+        <v>United States</v>
+      </c>
+      <c r="G1265" t="str">
+        <v>123456789456130</v>
+      </c>
+      <c r="H1265" t="str">
+        <v>VISA</v>
+      </c>
+      <c r="I1265" t="str">
+        <v>Arlington</v>
+      </c>
+      <c r="J1265" t="str">
+        <v>123 Ave</v>
+      </c>
+      <c r="K1265" t="str">
+        <v>United States</v>
+      </c>
+      <c r="L1265" t="str">
+        <v>Unq216891162US</v>
+      </c>
+      <c r="M1265" t="str">
+        <v>spring</v>
+      </c>
+      <c r="N1265" t="str">
+        <v>9 $</v>
+      </c>
+      <c r="O1265" t="str">
+        <v>2025-12-17T16:25:15.737Z</v>
+      </c>
+      <c r="P1265" t="str">
+        <v>2025-12-17T16:25:15.737Z</v>
+      </c>
+      <c r="Q1265">
+        <v>1</v>
+      </c>
+      <c r="R1265" t="str">
+        <v>US</v>
+      </c>
+      <c r="S1265" t="str">
+        <v xml:space="preserve"> United States</v>
+      </c>
+      <c r="T1265" t="str">
+        <v>789456123</v>
+      </c>
+      <c r="U1265" t="str">
+        <v>test2@gmail.com</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266">
+        <v>1133</v>
+      </c>
+      <c r="B1266" t="str">
+        <v>test</v>
+      </c>
+      <c r="C1266" t="str">
+        <v/>
+      </c>
+      <c r="D1266" t="str">
+        <v xml:space="preserve">123 Ave </v>
+      </c>
+      <c r="E1266" t="str">
+        <v>Arlington</v>
+      </c>
+      <c r="F1266" t="str">
+        <v>United States</v>
+      </c>
+      <c r="G1266" t="str">
+        <v>123456789456130</v>
+      </c>
+      <c r="H1266" t="str">
+        <v>VISA</v>
+      </c>
+      <c r="I1266" t="str">
+        <v>Arlington</v>
+      </c>
+      <c r="J1266" t="str">
+        <v>123 Ave</v>
+      </c>
+      <c r="K1266" t="str">
+        <v>United States</v>
+      </c>
+      <c r="L1266" t="str">
+        <v>Unq216891162US</v>
+      </c>
+      <c r="M1266" t="str">
+        <v>Tax (7%)</v>
+      </c>
+      <c r="N1266" t="str">
+        <v>0.63 $</v>
+      </c>
+      <c r="O1266" t="str">
+        <v>2025-12-17T16:25:15.737Z</v>
+      </c>
+      <c r="P1266" t="str">
+        <v>2025-12-17T16:25:15.737Z</v>
+      </c>
+      <c r="Q1266">
+        <v>1</v>
+      </c>
+      <c r="R1266" t="str">
+        <v>United States</v>
+      </c>
+      <c r="S1266" t="str">
+        <v>United States</v>
+      </c>
+      <c r="T1266" t="str">
+        <v>789456123</v>
+      </c>
+      <c r="U1266" t="str">
+        <v>test2@gmail.com</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267">
+        <v>1133</v>
+      </c>
+      <c r="B1267" t="str">
+        <v>test</v>
+      </c>
+      <c r="C1267" t="str">
+        <v/>
+      </c>
+      <c r="D1267" t="str">
+        <v xml:space="preserve">123 Ave </v>
+      </c>
+      <c r="E1267" t="str">
+        <v>Arlington</v>
+      </c>
+      <c r="F1267" t="str">
+        <v>United States</v>
+      </c>
+      <c r="G1267" t="str">
+        <v>123456789456130</v>
+      </c>
+      <c r="H1267" t="str">
+        <v>VISA</v>
+      </c>
+      <c r="I1267" t="str">
+        <v>Arlington</v>
+      </c>
+      <c r="J1267" t="str">
+        <v>123 Ave</v>
+      </c>
+      <c r="K1267" t="str">
+        <v>United States</v>
+      </c>
+      <c r="L1267" t="str">
+        <v>Unq216891162US</v>
+      </c>
+      <c r="M1267" t="str">
+        <v>Delivery Charge</v>
+      </c>
+      <c r="N1267" t="str">
+        <v>11.93 $</v>
+      </c>
+      <c r="O1267" t="str">
+        <v>2025-12-17T16:25:15.737Z</v>
+      </c>
+      <c r="P1267" t="str">
+        <v>2025-12-17T16:25:15.737Z</v>
+      </c>
+      <c r="Q1267">
+        <v>1</v>
+      </c>
+      <c r="R1267" t="str">
+        <v>United States</v>
+      </c>
+      <c r="S1267" t="str">
+        <v>United States</v>
+      </c>
+      <c r="T1267" t="str">
+        <v>789456123</v>
+      </c>
+      <c r="U1267" t="str">
+        <v>test2@gmail.com</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268">
+        <v>1134</v>
+      </c>
+      <c r="B1268" t="str">
+        <v>Vishal</v>
+      </c>
+      <c r="C1268" t="str">
+        <v>Puri</v>
+      </c>
+      <c r="D1268" t="str">
+        <v>607 Summit AVE APT</v>
+      </c>
+      <c r="E1268" t="str">
+        <v>Arlington</v>
+      </c>
+      <c r="F1268" t="str">
+        <v>US</v>
+      </c>
+      <c r="G1268" t="str">
+        <v/>
+      </c>
+      <c r="H1268" t="str">
+        <v/>
+      </c>
+      <c r="I1268" t="str">
+        <v/>
+      </c>
+      <c r="J1268" t="str">
+        <v/>
+      </c>
+      <c r="K1268" t="str">
+        <v>US</v>
+      </c>
+      <c r="L1268" t="str">
+        <v>Unq390646258US</v>
+      </c>
+      <c r="M1268" t="str">
+        <v>Account Setup</v>
+      </c>
+      <c r="N1268" t="str">
+        <v>0 $</v>
+      </c>
+      <c r="O1268" t="str">
+        <v>2026-03-23T19:15:09.809Z</v>
+      </c>
+      <c r="P1268" t="str">
+        <v>2026-03-23T19:15:09.809Z</v>
+      </c>
+      <c r="Q1268">
+        <v>0</v>
+      </c>
+      <c r="R1268" t="str">
+        <v>US</v>
+      </c>
+      <c r="S1268" t="str">
+        <v>US</v>
+      </c>
+      <c r="T1268" t="str">
+        <v>6823917228</v>
+      </c>
+      <c r="U1268" t="str">
+        <v>purivishal2800@gmail.com</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U1259"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U1268"/>
   </ignoredErrors>
 </worksheet>
 </file>